--- a/data/trans_bre/P2C_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,48</t>
+          <t>2,18; 12,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 10,52</t>
+          <t>-0,08; 10,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 8,38</t>
+          <t>-1,84; 9,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 6,63</t>
+          <t>-1,48; 6,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 43,74</t>
+          <t>6,77; 43,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 23,83</t>
+          <t>-0,18; 24,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 27,03</t>
+          <t>-5,42; 28,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 59,83</t>
+          <t>-9,76; 61,17</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,01</t>
+          <t>-0,14; 8,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 11,56</t>
+          <t>2,33; 11,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,58</t>
+          <t>5,24; 13,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 17,4</t>
+          <t>6,15; 16,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 28,1</t>
+          <t>-0,6; 29,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 25,26</t>
+          <t>4,41; 24,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,03; 43,01</t>
+          <t>14,81; 44,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,0; 285,87</t>
+          <t>38,94; 261,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,71</t>
+          <t>-0,0; 9,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 13,87</t>
+          <t>2,96; 14,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 13,81</t>
+          <t>3,88; 13,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 52,48</t>
+          <t>3,25; 55,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 37,51</t>
+          <t>0,26; 38,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 33,06</t>
+          <t>6,35; 34,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 47,76</t>
+          <t>11,19; 48,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,36; 605,11</t>
+          <t>26,05; 565,93</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,85</t>
+          <t>1,51; 10,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 11,6</t>
+          <t>2,67; 11,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,65</t>
+          <t>3,52; 11,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,34</t>
+          <t>-2,48; 4,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 39,97</t>
+          <t>5,16; 39,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 31,55</t>
+          <t>6,58; 31,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 46,99</t>
+          <t>11,83; 48,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 43,72</t>
+          <t>-18,58; 40,71</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,64</t>
+          <t>3,11; 7,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,63</t>
+          <t>4,44; 9,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,87</t>
+          <t>5,2; 9,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 24,36</t>
+          <t>4,08; 24,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,83; 27,14</t>
+          <t>10,26; 27,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 22,37</t>
+          <t>9,73; 21,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,69; 33,01</t>
+          <t>15,81; 32,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,74; 208,36</t>
+          <t>31,86; 234,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,28</t>
+          <t>2,16; 12,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 10,75</t>
+          <t>-0,05; 10,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 9,0</t>
+          <t>-1,75; 8,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 6,73</t>
+          <t>0,48; 7,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 43,57</t>
+          <t>5,83; 42,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 24,54</t>
+          <t>-0,37; 24,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 28,58</t>
+          <t>-4,67; 26,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 61,17</t>
+          <t>2,47; 67,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,35</t>
+          <t>-0,3; 8,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,48</t>
+          <t>2,72; 11,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,71</t>
+          <t>4,7; 13,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,91</t>
+          <t>2,42; 9,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 29,18</t>
+          <t>-0,92; 31,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,86</t>
+          <t>5,25; 25,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 44,21</t>
+          <t>12,93; 45,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,94; 261,95</t>
+          <t>12,56; 63,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>204,22%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 9,99</t>
+          <t>0,05; 10,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 14,15</t>
+          <t>2,94; 13,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,73</t>
+          <t>3,55; 13,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 55,74</t>
+          <t>2,53; 9,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 38,47</t>
+          <t>-0,12; 38,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 34,05</t>
+          <t>6,25; 32,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 48,32</t>
+          <t>10,55; 48,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 565,93</t>
+          <t>18,26; 96,16</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 10,01</t>
+          <t>1,78; 10,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 11,43</t>
+          <t>2,46; 11,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,96</t>
+          <t>3,36; 11,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 4,12</t>
+          <t>-0,68; 5,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 39,78</t>
+          <t>6,29; 40,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 31,37</t>
+          <t>5,99; 31,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 48,09</t>
+          <t>11,89; 47,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 40,71</t>
+          <t>-4,95; 48,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,68</t>
+          <t>3,04; 7,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 9,13</t>
+          <t>4,29; 9,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,97</t>
+          <t>5,07; 9,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 24,31</t>
+          <t>2,87; 6,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,26; 27,4</t>
+          <t>10,01; 28,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 21,1</t>
+          <t>9,28; 20,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,81; 32,61</t>
+          <t>15,87; 31,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,86; 234,0</t>
+          <t>19,5; 49,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R2-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
